--- a/artfynd/A 31151-2022 artfynd.xlsx
+++ b/artfynd/A 31151-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31151-2022 artfynd.xlsx
+++ b/artfynd/A 31151-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70652352</v>
+        <v>73570702</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Revlummer 2, Vrm</t>
+          <t>Lorensberg, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417037.2768349831</v>
+        <v>417143</v>
       </c>
       <c r="R2" t="n">
-        <v>6587133.805900953</v>
+        <v>6586987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2018-10-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2018-10-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +778,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Tall-gran äldre skog; flera granbarkborre angripna stående träd finns in området</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -798,15 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70652302</v>
+        <v>103391505</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,23 +837,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Revlummer 1, Vrm</t>
+          <t>Stockfallet, Karlstad kommun, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417087.2211610316</v>
+        <v>417072</v>
       </c>
       <c r="R3" t="n">
-        <v>6587039.022147211</v>
+        <v>6587096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,22 +889,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,15 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70847179</v>
+        <v>108876504</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,48 +942,57 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stocktallet, Vrm</t>
+          <t>Lorensberg, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417218.3884922367</v>
+        <v>417105</v>
       </c>
       <c r="R4" t="n">
-        <v>6586879.825260133</v>
+        <v>6587011</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +1016,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-04-24</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-04-24</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,11 +1042,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1049,65 +1058,77 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73570702</v>
+        <v>100106178</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lorensberg, Vrm</t>
+          <t>Karlstad, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>417143.2042071945</v>
+        <v>417048</v>
       </c>
       <c r="R5" t="n">
-        <v>6586986.875789084</v>
+        <v>6587357</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,67 +1152,57 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-10-15</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-10-15</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Tall-gran äldre skog; flera granbarkborre angripna stående träd finns in området</t>
+          <t>Bäck</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ewa Orlikowska</t>
+          <t>Mattias Almroth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ewa Orlikowska</t>
+          <t>Mattias Almroth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103391740</v>
+        <v>70652302</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1229,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1228,21 +1239,16 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stockfallet, Vrm</t>
+          <t>Revlummer 1, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417090.4629253168</v>
+        <v>417087</v>
       </c>
       <c r="R6" t="n">
-        <v>6587070.519668573</v>
+        <v>6587039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,7 +1275,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1279,7 +1285,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1293,7 +1299,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1312,70 +1317,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103391505</v>
+        <v>70652352</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stockfallet, Karlstad kommun, Vrm</t>
+          <t>Revlummer 2, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417072.1585797733</v>
+        <v>417037</v>
       </c>
       <c r="R7" t="n">
-        <v>6587096.379970566</v>
+        <v>6587134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,22 +1393,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,15 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103391722</v>
+        <v>103391740</v>
       </c>
       <c r="B8" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,16 +1446,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1479,7 +1465,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1496,14 +1482,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockfallet, Karlstad kommun, Vrm</t>
+          <t>Stockfallet, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417057.0766517741</v>
+        <v>417091</v>
       </c>
       <c r="R8" t="n">
-        <v>6587106.385323476</v>
+        <v>6587071</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1576,12 +1562,7 @@
         <v>103645663</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,10 +1608,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417083.8535553748</v>
+        <v>417084</v>
       </c>
       <c r="R9" t="n">
-        <v>6587048.261208426</v>
+        <v>6587048</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1699,73 +1680,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108876504</v>
+        <v>70847179</v>
       </c>
       <c r="B10" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lorensberg, Vrm</t>
+          <t>Stocktallet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>417105.4700464449</v>
+        <v>417218</v>
       </c>
       <c r="R10" t="n">
-        <v>6587010.616874032</v>
+        <v>6586880</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1789,22 +1756,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2018-04-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2018-04-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1815,6 +1772,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1828,6 +1790,130 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103391722</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stockfallet, Karlstad kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>417057</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6587106</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ewa Orlikowska</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ewa Orlikowska</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31151-2022 artfynd.xlsx
+++ b/artfynd/A 31151-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103391505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108876504</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1067,6 +1082,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100106178</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1185,6 +1205,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70652302</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1303,6 +1328,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70652352</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1427,6 +1457,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103391740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1548,6 +1583,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103645663</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103391722</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1801,6 +1846,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73570702</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1914,8 +1964,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70847179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>